--- a/temp/pages/StructureDefinition-MyPatient.xlsx
+++ b/temp/pages/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T16:23:10-04:00</t>
+    <t>2025-07-27T11:31:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/temp/pages/StructureDefinition-MyPatient.xlsx
+++ b/temp/pages/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T11:31:10-04:00</t>
+    <t>2025-07-27T11:33:37-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/temp/pages/StructureDefinition-MyPatient.xlsx
+++ b/temp/pages/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T11:33:37-04:00</t>
+    <t>2025-07-27T15:07:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/temp/pages/StructureDefinition-MyPatient.xlsx
+++ b/temp/pages/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-27T15:07:55-04:00</t>
+    <t>2025-07-28T11:44:01-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
